--- a/Config/Datas/Tables/d_动画片段_AnimationClipConfig.xlsx
+++ b/Config/Datas/Tables/d_动画片段_AnimationClipConfig.xlsx
@@ -22178,7 +22178,7 @@
         <x:v>320004</x:v>
       </x:c>
       <x:c r="E889" s="95" t="str">
-        <x:v>Unused</x:v>
+        <x:v>CastEffect</x:v>
       </x:c>
       <x:c r="F889" s="95" t="str">
         <x:v>s</x:v>
@@ -23098,8 +23098,8 @@
       <x:c r="G927" s="97" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H927" s="97" t="b">
-        <x:v>0</x:v>
+      <x:c r="H927" s="97" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="928">
@@ -23138,7 +23138,7 @@
         <x:v>320044</x:v>
       </x:c>
       <x:c r="E929" s="95" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>CastEffect</x:v>
       </x:c>
       <x:c r="F929" s="95" t="str">
         <x:v>s</x:v>
@@ -23314,8 +23314,8 @@
       <x:c r="G936" s="97" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H936" s="97" t="b">
-        <x:v>0</x:v>
+      <x:c r="H936" s="97" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="937">
@@ -23354,7 +23354,7 @@
         <x:v>320053</x:v>
       </x:c>
       <x:c r="E938" s="95" t="str">
-        <x:v>Unused</x:v>
+        <x:v>CastEffect</x:v>
       </x:c>
       <x:c r="F938" s="95" t="str">
         <x:v>s</x:v>
@@ -23674,8 +23674,8 @@
       <x:c r="G951" s="97" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H951" s="97" t="b">
-        <x:v>0</x:v>
+      <x:c r="H951" s="97" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="952">
@@ -23698,8 +23698,8 @@
       <x:c r="G952" s="97" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H952" s="97" t="b">
-        <x:v>0</x:v>
+      <x:c r="H952" s="97" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="953">
@@ -23738,7 +23738,7 @@
         <x:v>320069</x:v>
       </x:c>
       <x:c r="E954" s="95" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>CastEffect</x:v>
       </x:c>
       <x:c r="F954" s="95" t="str">
         <x:v>s</x:v>
@@ -23930,16 +23930,16 @@
         <x:v>320078</x:v>
       </x:c>
       <x:c r="E962" s="95" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Projectile</x:v>
       </x:c>
       <x:c r="F962" s="95" t="str">
         <x:v>f</x:v>
       </x:c>
-      <x:c r="G962" s="97" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H962" s="97" t="b">
-        <x:v>0</x:v>
+      <x:c r="G962" s="97" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H962" s="97" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="963">
@@ -23954,7 +23954,7 @@
         <x:v>320079</x:v>
       </x:c>
       <x:c r="E963" s="95" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Impact</x:v>
       </x:c>
       <x:c r="F963" s="95" t="str">
         <x:v>h</x:v>
@@ -23978,7 +23978,7 @@
         <x:v>320080</x:v>
       </x:c>
       <x:c r="E964" s="95" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>CastEffect</x:v>
       </x:c>
       <x:c r="F964" s="95" t="str">
         <x:v>s</x:v>
@@ -24410,7 +24410,7 @@
         <x:v>320098</x:v>
       </x:c>
       <x:c r="E982" s="95" t="str">
-        <x:v>Unknown</x:v>
+        <x:v>Area</x:v>
       </x:c>
       <x:c r="F982" s="95" t="str">
         <x:v>h</x:v>
